--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G262"/>
+  <dimension ref="A1:G264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2977,12 +2977,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,17 +3310,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -3397,12 +3397,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3432,12 +3432,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3537,12 +3537,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3572,12 +3572,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3607,12 +3607,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3642,12 +3642,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3887,12 +3887,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4097,12 +4097,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4237,12 +4237,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4692,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4937,12 +4937,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4972,12 +4972,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5217,12 +5217,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,34 +5270,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5322,17 +5322,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5707,12 +5707,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7037,12 +7037,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7282,12 +7282,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7632,12 +7632,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,17 +7650,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -7702,12 +7702,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -8122,12 +8122,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -8682,12 +8682,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -9067,12 +9067,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -9277,12 +9277,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -9312,12 +9312,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -9557,33 +9557,103 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
           <t>RAI WAY SPA</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>RAI WAY</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>1</v>
-      </c>
-      <c r="E262" t="inlineStr">
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" t="inlineStr">
         <is>
           <t>RAI WAY</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
+      <c r="F264" t="inlineStr">
         <is>
           <t>RAI WAY SPA</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G264" t="inlineStr">
         <is>
           <t>Roma Aurelia</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G264"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5147,12 +5147,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5217,12 +5217,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5322,17 +5322,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,34 +5375,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5847,12 +5847,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5987,12 +5987,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6302,12 +6302,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,17 +6460,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -6512,12 +6512,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7072,12 +7072,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7422,12 +7422,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7912,12 +7912,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7947,12 +7947,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -8017,12 +8017,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -8752,12 +8752,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,50 +9610,155 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
           <t>RAI WAY SPA</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>RAI WAY</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>1</v>
-      </c>
-      <c r="E264" t="inlineStr">
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1</v>
+      </c>
+      <c r="E267" t="inlineStr">
         <is>
           <t>RAI WAY</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F267" t="inlineStr">
         <is>
           <t>RAI WAY SPA</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G267" t="inlineStr">
         <is>
           <t>Roma Aurelia</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G267"/>
+  <dimension ref="A1:G271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8402,12 +8402,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -8507,12 +8507,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -8577,12 +8577,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,17 +8665,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,12 +8945,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -8962,12 +8962,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,50 +9715,190 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>RAI WAY SPA</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>RAI WAY</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>1</v>
-      </c>
-      <c r="E267" t="inlineStr">
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" t="inlineStr">
         <is>
           <t>RAI WAY</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
+      <c r="F271" t="inlineStr">
         <is>
           <t>RAI WAY SPA</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G271" t="inlineStr">
         <is>
           <t>Roma Aurelia</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3012,12 +3012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>D2M GREEN ENERGY FIUMETTO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>D2M GREEN ENERGY FIUMETTO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,17 +3345,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3572,12 +3572,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3607,12 +3607,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3642,12 +3642,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3677,12 +3677,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,17 +4675,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4972,12 +4972,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5007,12 +5007,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5392,17 +5392,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,34 +5445,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5917,12 +5917,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6057,12 +6057,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6372,12 +6372,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,17 +6530,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6582,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -7142,12 +7142,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7492,12 +7492,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7982,12 +7982,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -8017,12 +8017,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -8087,12 +8087,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -8857,12 +8857,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -9067,12 +9067,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -9872,35 +9872,175 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
           <t>RAI WAY SPA</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>RAI WAY</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" t="inlineStr">
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" t="inlineStr">
         <is>
           <t>RAI WAY</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F274" t="inlineStr">
         <is>
           <t>RAI WAY SPA</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
+      <c r="G274" t="inlineStr">
         <is>
           <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>SOLAR PV 1 SRL</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G275"/>
+  <dimension ref="A1:G299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1227,12 +1227,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>COGEME NUOVE ENERGIE SRL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>COGEME NUOVE ENERGIE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1245,29 +1245,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>COGEME NUOVE ENERGIE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>COGEME NUOVE ENERGIE SRL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1280,29 +1280,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>TRINA SOLAR TOSCANA 1 SRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>TRINA SOLAR TOSCANA 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>TRINA SOLAR TOSCANA 1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>TRINA SOLAR TOSCANA 1 SRL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>SORGENIA PEGASO SRL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>SORGENIA PEGASO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1350,29 +1350,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>SORGENIA PEGASO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>SORGENIA PEGASO SRL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>APOLLO SOLAR 7 SRL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>APOLLO SOLAR 7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1385,29 +1385,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>APOLLO SOLAR 7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>APOLLO SOLAR 7 SRL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>LUNER INVEST SRL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>LUNER INVEST</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1420,29 +1420,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>LUNER INVEST</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>LUNER INVEST SRL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>REVALUE PV 2 SRL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>REVALUE PV 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1455,29 +1455,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>REVALUE PV 2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>REVALUE PV 2 SRL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>SORGENIA GREEN SOLUTIONS SRL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>SORGENIA GREEN SOLUTIONS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1490,29 +1490,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>SORGENIA GREEN SOLUTIONS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>SORGENIA GREEN SOLUTIONS SRL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1560,29 +1560,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1595,29 +1595,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1665,29 +1665,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1700,29 +1700,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1840,29 +1840,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1875,29 +1875,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CCE ITALIA</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CCE ITALIA SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,29 +1945,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,29 +1980,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>CCE ITALIA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>CCE ITALIA SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2382,12 +2382,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,29 +2470,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,29 +2505,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,29 +2540,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,29 +2575,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>XELIO ANTARES SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>XELIO ANTARES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>XELIO ANTARES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>XELIO ANTARES SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2627,12 +2627,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES CARLENTINI PV</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,29 +2680,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES CARLENTINI PV</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,29 +2715,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FRANCOFONTE SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FRANCOFONTE</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FRANCOFONTE</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FRANCOFONTE SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CHERRY PICKING SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CHERRY PICKING</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CHERRY PICKING</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CHERRY PICKING SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FOREARTH SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FOREARTH</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FOREARTH</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FOREARTH SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY SRL</t>
+          <t>DREN SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY</t>
+          <t>DREN SOLARE 10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY</t>
+          <t>DREN SOLARE 10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY SRL</t>
+          <t>DREN SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE SRL</t>
+          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE</t>
+          <t>TEP RENEWABLES CARLENTINI PV</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE</t>
+          <t>TEP RENEWABLES CARLENTINI PV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE SRL</t>
+          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
+          <t>FRANCOFONTE SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY FIUMETTO</t>
+          <t>FRANCOFONTE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY FIUMETTO</t>
+          <t>FRANCOFONTE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
+          <t>FRANCOFONTE SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>CHERRY PICKING SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>CHERRY PICKING</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>CHERRY PICKING</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>CHERRY PICKING SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SICILY MON P1 DEV SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SICILY MON P1 DEV</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SICILY MON P1 DEV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SICILY MON P1 DEV SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>LUMINORA SERRAVALLE SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>LUMINORA SERRAVALLE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>LUMINORA SERRAVALLE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>LUMINORA SERRAVALLE SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FOREARTH SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FOREARTH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FOREARTH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FOREARTH SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>TOLALP ENERGY SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>TOLALP ENERGY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>TOLALP ENERGY</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>TOLALP ENERGY SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>INNOVAZIONE AGRISOLARE SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>INNOVAZIONE AGRISOLARE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>INNOVAZIONE AGRISOLARE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>INNOVAZIONE AGRISOLARE SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3257,12 +3257,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>D2M GREEN ENERGY FIUMETTO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>D2M GREEN ENERGY FIUMETTO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>EDERA SOL SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>EDERA SOL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>EDERA SOL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>EDERA SOL SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>VATT ENERGY SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>VATT ENERGY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>VATT ENERGY</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>VATT ENERGY SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3397,12 +3397,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4447,12 +4447,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4622,12 +4622,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4972,12 +4972,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5217,12 +5217,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5357,12 +5357,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5392,12 +5392,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,34 +5445,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,34 +5935,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6547,12 +6547,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7002,12 +7002,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7037,12 +7037,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7107,12 +7107,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7772,12 +7772,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7982,12 +7982,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,12 +8980,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -8997,12 +8997,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -9382,12 +9382,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,12 +9470,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -9487,12 +9487,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -9697,12 +9697,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -9872,12 +9872,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,29 +9925,29 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -9977,12 +9977,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,50 +9995,890 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
+          <t>AIEM GREEN SRL</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>AIEM GREEN</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>AIEM GREEN</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>AIEM GREEN SRL</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Padova</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>SCOTTA SPA</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>SCOTTA</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>1</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>SCOTTA</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>SCOTTA SPA</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY ITALIA SRL</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>1</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY ITALIA SRL</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ATLAS SOLAR 13 SRL</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>ATLAS SOLAR 13</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>ATLAS SOLAR 13</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>ATLAS SOLAR 13 SRL</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>DOLOMITI MERCATO</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>1</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>DOLOMITI MERCATO</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Trento</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>RERE 62 SRL</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>RERE 62</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>RERE 62</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>RERE 62 SRL</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>AMBRA SOLARE 29 SRL</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>AMBRA SOLARE 29</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>1</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>AMBRA SOLARE 29</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>AMBRA SOLARE 29 SRL</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Roma Nomentana</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>1</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>1</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>PSG ENERGY SYSTEM SRL</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>PSG ENERGY SYSTEM</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>1</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>PSG ENERGY SYSTEM</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>PSG ENERGY SYSTEM SRL</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>MARMARIA SOLARE 9 SRL</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>MARMARIA SOLARE 9</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>MARMARIA SOLARE 9</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>MARMARIA SOLARE 9 SRL</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Roma Nomentana</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>1</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>1</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>1</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>1</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>1</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>1</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>1</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>1</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D275" t="n">
-        <v>1</v>
-      </c>
-      <c r="E275" t="inlineStr">
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>1</v>
+      </c>
+      <c r="E299" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
+      <c r="F299" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
+      <c r="G299" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G299"/>
+  <dimension ref="A1:G300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1507,12 +1507,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>VOLT 9 SRL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>VOLT 9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>VOLT 9</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>VOLT 9 SRL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1560,29 +1560,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1595,29 +1595,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1665,29 +1665,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1840,29 +1840,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1892,12 +1892,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1962,12 +1962,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1997,12 +1997,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CCE ITALIA</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CCE ITALIA SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>CCE ITALIA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>CCE ITALIA SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2312,12 +2312,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,29 +2470,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,29 +2505,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,29 +2540,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,29 +2575,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2627,12 +2627,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>XELIO ANTARES SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>XELIO ANTARES</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>XELIO ANTARES</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>XELIO ANTARES SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10 SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10 SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
+          <t>DREN SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES CARLENTINI PV</t>
+          <t>DREN SOLARE 10</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES CARLENTINI PV</t>
+          <t>DREN SOLARE 10</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
+          <t>DREN SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA SRL</t>
+          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA</t>
+          <t>TEP RENEWABLES CARLENTINI PV</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA</t>
+          <t>TEP RENEWABLES CARLENTINI PV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA SRL</t>
+          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FRANCOFONTE SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRANCOFONTE</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FRANCOFONTE</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FRANCOFONTE SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHERRY PICKING SRL</t>
+          <t>FRANCOFONTE SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CHERRY PICKING</t>
+          <t>FRANCOFONTE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CHERRY PICKING</t>
+          <t>FRANCOFONTE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CHERRY PICKING SRL</t>
+          <t>FRANCOFONTE SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3082,12 +3082,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV SRL</t>
+          <t>CHERRY PICKING SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV</t>
+          <t>CHERRY PICKING</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV</t>
+          <t>CHERRY PICKING</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV SRL</t>
+          <t>CHERRY PICKING SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE SRL</t>
+          <t>SICILY MON P1 DEV SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE</t>
+          <t>SICILY MON P1 DEV</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE</t>
+          <t>SICILY MON P1 DEV</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE SRL</t>
+          <t>SICILY MON P1 DEV SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FOREARTH SRL</t>
+          <t>LUMINORA SERRAVALLE SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FOREARTH</t>
+          <t>LUMINORA SERRAVALLE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FOREARTH</t>
+          <t>LUMINORA SERRAVALLE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FOREARTH SRL</t>
+          <t>LUMINORA SERRAVALLE SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY SRL</t>
+          <t>FOREARTH SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY</t>
+          <t>FOREARTH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY</t>
+          <t>FOREARTH</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY SRL</t>
+          <t>FOREARTH SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE SRL</t>
+          <t>TOLALP ENERGY SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE</t>
+          <t>TOLALP ENERGY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE</t>
+          <t>TOLALP ENERGY</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE SRL</t>
+          <t>TOLALP ENERGY SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>INNOVAZIONE AGRISOLARE SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>INNOVAZIONE AGRISOLARE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>INNOVAZIONE AGRISOLARE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>INNOVAZIONE AGRISOLARE SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY FIUMETTO</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY FIUMETTO</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EDERA SOL SRL</t>
+          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EDERA SOL</t>
+          <t>D2M GREEN ENERGY FIUMETTO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EDERA SOL</t>
+          <t>D2M GREEN ENERGY FIUMETTO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>EDERA SOL SRL</t>
+          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VATT ENERGY SRL</t>
+          <t>EDERA SOL SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VATT ENERGY</t>
+          <t>EDERA SOL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>VATT ENERGY</t>
+          <t>EDERA SOL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>VATT ENERGY SRL</t>
+          <t>EDERA SOL SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>VATT ENERGY SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>VATT ENERGY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>VATT ENERGY</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>VATT ENERGY SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3817,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4027,12 +4027,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4307,12 +4307,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,17 +5060,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -5112,12 +5112,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5357,12 +5357,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5392,12 +5392,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5777,12 +5777,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5882,12 +5882,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,34 +5935,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5987,17 +5987,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6372,12 +6372,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7947,12 +7947,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -8192,12 +8192,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -8542,12 +8542,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,17 +8560,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -9102,12 +9102,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -9312,12 +9312,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -9417,12 +9417,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,17 +9435,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -9487,12 +9487,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,17 +9610,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
@@ -9662,12 +9662,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,29 +9855,29 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -9907,12 +9907,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,29 +9925,29 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,29 +9960,29 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -10012,12 +10012,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,29 +10030,29 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10100,29 +10100,29 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10135,29 +10135,29 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10170,29 +10170,29 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10205,29 +10205,29 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,29 +10310,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,29 +10345,29 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,29 +10380,29 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,29 +10415,29 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,29 +10450,29 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,29 +10485,29 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,29 +10520,29 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,29 +10555,29 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,29 +10590,29 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,50 +10835,85 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>1</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>1</v>
-      </c>
-      <c r="E299" t="inlineStr">
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1</v>
+      </c>
+      <c r="E300" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
+      <c r="F300" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
+      <c r="G300" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G300"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9207,12 +9207,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,12 +9225,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -9242,12 +9242,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -9347,12 +9347,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -9452,12 +9452,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,17 +9470,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,17 +9645,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
@@ -9697,12 +9697,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,29 +9855,29 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,12 +9925,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -9942,12 +9942,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,29 +9960,29 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,29 +9995,29 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -10047,12 +10047,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10100,29 +10100,29 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10135,29 +10135,29 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10170,29 +10170,29 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10205,29 +10205,29 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,29 +10310,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,29 +10345,29 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,29 +10380,29 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,29 +10415,29 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,29 +10450,29 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,29 +10485,29 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,29 +10520,29 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,29 +10555,29 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,29 +10590,29 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,29 +10835,29 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10870,50 +10870,85 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D300" t="n">
-        <v>1</v>
-      </c>
-      <c r="E300" t="inlineStr">
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1</v>
+      </c>
+      <c r="E301" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
+      <c r="F301" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
+      <c r="G301" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:G310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1542,12 +1542,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>IDROAGRI SOC AGRICOLA SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>IDROAGRI AGRICOLA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1560,29 +1560,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>IDROAGRI AGRICOLA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>IDROAGRI SOC AGRICOLA SRL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Genova</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>SPD TRE SRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>SPD TRE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1595,29 +1595,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>SPD TRE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>SPD TRE SRL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1647,12 +1647,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1665,29 +1665,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1840,29 +1840,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1875,29 +1875,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,29 +1945,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,29 +1980,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CCE ITALIA</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CCE ITALIA SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CCE ITALIA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CCE ITALIA SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,29 +2470,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,29 +2505,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,29 +2540,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,29 +2575,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,29 +2610,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,29 +2680,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,29 +2715,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2872,12 +2872,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>XELIO ANTARES SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>XELIO ANTARES</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>XELIO ANTARES</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>XELIO ANTARES SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10 SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DREN SOLARE 10 SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES CARLENTINI PV</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES CARLENTINI PV</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA SRL</t>
+          <t>DREN SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA</t>
+          <t>DREN SOLARE 10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA</t>
+          <t>DREN SOLARE 10</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RENANTIS SICILIA SRL</t>
+          <t>DREN SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FRANCOFONTE SRL</t>
+          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FRANCOFONTE</t>
+          <t>TEP RENEWABLES CARLENTINI PV</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FRANCOFONTE</t>
+          <t>TEP RENEWABLES CARLENTINI PV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FRANCOFONTE SRL</t>
+          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHERRY PICKING SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CHERRY PICKING</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CHERRY PICKING</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CHERRY PICKING SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV SRL</t>
+          <t>FRANCOFONTE SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV</t>
+          <t>FRANCOFONTE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV</t>
+          <t>FRANCOFONTE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SICILY MON P1 DEV SRL</t>
+          <t>FRANCOFONTE SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE SRL</t>
+          <t>CHERRY PICKING SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE</t>
+          <t>CHERRY PICKING</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE</t>
+          <t>CHERRY PICKING</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LUMINORA SERRAVALLE SRL</t>
+          <t>CHERRY PICKING SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FOREARTH SRL</t>
+          <t>SICILY MON P1 DEV SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FOREARTH</t>
+          <t>SICILY MON P1 DEV</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FOREARTH</t>
+          <t>SICILY MON P1 DEV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FOREARTH SRL</t>
+          <t>SICILY MON P1 DEV SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY SRL</t>
+          <t>LUMINORA SERRAVALLE SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY</t>
+          <t>LUMINORA SERRAVALLE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY</t>
+          <t>LUMINORA SERRAVALLE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>TOLALP ENERGY SRL</t>
+          <t>LUMINORA SERRAVALLE SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE SRL</t>
+          <t>FOREARTH SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE</t>
+          <t>FOREARTH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE</t>
+          <t>FOREARTH</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>INNOVAZIONE AGRISOLARE SRL</t>
+          <t>FOREARTH SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>TOLALP ENERGY SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>TOLALP ENERGY</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>TOLALP ENERGY</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>TOLALP ENERGY SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
+          <t>INNOVAZIONE AGRISOLARE SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY FIUMETTO</t>
+          <t>INNOVAZIONE AGRISOLARE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY FIUMETTO</t>
+          <t>INNOVAZIONE AGRISOLARE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
+          <t>INNOVAZIONE AGRISOLARE SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EDERA SOL SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EDERA SOL</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>EDERA SOL</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>EDERA SOL SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3397,12 +3397,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VATT ENERGY SRL</t>
+          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VATT ENERGY</t>
+          <t>D2M GREEN ENERGY FIUMETTO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>VATT ENERGY</t>
+          <t>D2M GREEN ENERGY FIUMETTO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VATT ENERGY SRL</t>
+          <t>D2M GREEN ENERGY - FIUMETTO SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>EDERA SOL SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>EDERA SOL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>EDERA SOL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>EDERA SOL SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>VATT ENERGY SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>VATT ENERGY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>VATT ENERGY</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>VATT ENERGY SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>EPSILON GEMINI SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>EPSILON GEMINI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>EPSILON GEMINI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>EPSILON GEMINI SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3642,12 +3642,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3677,12 +3677,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3887,12 +3887,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4097,12 +4097,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4167,12 +4167,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4587,12 +4587,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4692,12 +4692,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4727,12 +4727,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5112,12 +5112,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5287,12 +5287,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5812,12 +5812,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>S2SE TRE SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>S2SE TRE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>S2SE TRE</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>S2SE TRE SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5952,12 +5952,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>EEC SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>EEC SOLAR 3</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,34 +5970,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>EEC SOLAR 3</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>EEC SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,34 +6145,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6442,12 +6442,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6757,12 +6757,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7597,12 +7597,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -9277,12 +9277,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -9312,12 +9312,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -9382,12 +9382,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -9802,12 +9802,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,29 +9855,29 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,29 +9925,29 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,29 +9960,29 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,29 +9995,29 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -10047,12 +10047,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10100,29 +10100,29 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10135,29 +10135,29 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -10187,12 +10187,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10205,29 +10205,29 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,29 +10310,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -10362,12 +10362,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,29 +10380,29 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,29 +10415,29 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,29 +10450,29 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,29 +10485,29 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,29 +10520,29 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,29 +10555,29 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -10607,12 +10607,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,29 +10835,29 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10905,50 +10905,365 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>1</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>1</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>1</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>1</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D301" t="n">
-        <v>1</v>
-      </c>
-      <c r="E301" t="inlineStr">
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1</v>
+      </c>
+      <c r="E310" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
+      <c r="F310" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
+      <c r="G310" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G310"/>
+  <dimension ref="A1:G315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3537,12 +3537,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>VELINO SOLAR ITALY SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>VELINO SOLAR</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>VELINO SOLAR</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>VELINO SOLAR ITALY SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3747,12 +3747,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4167,12 +4167,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4692,12 +4692,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4797,12 +4797,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5217,12 +5217,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5392,12 +5392,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5917,12 +5917,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S2SE TRE SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>S2SE TRE</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>S2SE TRE</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>S2SE TRE SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3 SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3 SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>S2SE TRE SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>S2SE TRE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>S2SE TRE</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>S2SE TRE SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>EEC SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>EEC SOLAR 3</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>EEC SOLAR 3</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>EEC SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6162,17 +6162,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6197,12 +6197,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,34 +6250,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6722,12 +6722,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6757,12 +6757,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -7352,12 +7352,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,17 +7580,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -7632,12 +7632,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7912,12 +7912,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -8157,12 +8157,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -8192,12 +8192,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -8402,12 +8402,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -9872,12 +9872,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,29 +9925,29 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,29 +9960,29 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,29 +9995,29 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,29 +10030,29 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10100,29 +10100,29 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10135,29 +10135,29 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10170,29 +10170,29 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -10222,12 +10222,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,12 +10310,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -10327,12 +10327,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -10362,12 +10362,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,29 +10380,29 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,12 +10415,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -10432,12 +10432,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,29 +10450,29 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,29 +10485,29 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,29 +10520,29 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,29 +10555,29 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,29 +10590,29 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -10852,12 +10852,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10905,29 +10905,29 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10940,29 +10940,29 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10975,29 +10975,29 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11010,29 +11010,29 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11045,29 +11045,29 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -11097,12 +11097,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11115,29 +11115,29 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11150,29 +11150,29 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11185,29 +11185,29 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11220,50 +11220,225 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>1</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>1</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>1</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D310" t="n">
-        <v>1</v>
-      </c>
-      <c r="E310" t="inlineStr">
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1</v>
+      </c>
+      <c r="E315" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
+      <c r="F315" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
+      <c r="G315" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G315"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11202,12 +11202,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11220,29 +11220,29 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11255,29 +11255,29 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11290,29 +11290,29 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11325,29 +11325,29 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11360,29 +11360,29 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11395,50 +11395,85 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D315" t="n">
-        <v>1</v>
-      </c>
-      <c r="E315" t="inlineStr">
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1</v>
+      </c>
+      <c r="E316" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
+      <c r="F316" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr">
+      <c r="G316" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3642,12 +3642,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,17 +3975,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4062,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4097,12 +4097,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4237,12 +4237,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4307,12 +4307,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4552,12 +4552,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,12 +4745,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4762,12 +4762,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4902,12 +4902,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,17 +5305,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -5357,12 +5357,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5637,12 +5637,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6022,12 +6022,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S2SE TRE SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>S2SE TRE</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>S2SE TRE</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>S2SE TRE SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3 SRL</t>
+          <t>S2SE TRE SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3</t>
+          <t>S2SE TRE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3</t>
+          <t>S2SE TRE</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3 SRL</t>
+          <t>S2SE TRE SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>EEC SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>EEC SOLAR 3</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>EEC SOLAR 3</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>EEC SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6197,12 +6197,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,34 +6250,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6302,17 +6302,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6687,12 +6687,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -8367,12 +8367,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -8612,12 +8612,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,12 +8945,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -8962,12 +8962,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,17 +8980,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -9032,12 +9032,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -9522,12 +9522,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -9662,12 +9662,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -9872,12 +9872,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,17 +9890,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -9942,12 +9942,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,29 +9960,29 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,29 +9995,29 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,29 +10030,29 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,17 +10065,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
@@ -10117,12 +10117,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10135,29 +10135,29 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10170,29 +10170,29 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10205,29 +10205,29 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,29 +10310,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -10362,12 +10362,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,29 +10380,29 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,29 +10415,29 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -10467,12 +10467,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,29 +10485,29 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,29 +10520,29 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,29 +10555,29 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,29 +10590,29 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,29 +10835,29 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10905,29 +10905,29 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10940,29 +10940,29 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10975,29 +10975,29 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11010,29 +11010,29 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11045,29 +11045,29 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11080,29 +11080,29 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11115,29 +11115,29 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11150,29 +11150,29 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11185,29 +11185,29 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11220,29 +11220,29 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11255,29 +11255,29 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11290,29 +11290,29 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11325,29 +11325,29 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11360,29 +11360,29 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11395,29 +11395,29 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11430,50 +11430,85 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D316" t="n">
-        <v>1</v>
-      </c>
-      <c r="E316" t="inlineStr">
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1</v>
+      </c>
+      <c r="E317" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
+      <c r="F317" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
+      <c r="G317" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G317"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6127,12 +6127,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>INE NARDO' SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>INE NARDO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>INE NARDO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>INE NARDO' SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6232,12 +6232,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,34 +6285,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6337,17 +6337,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6722,12 +6722,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -8402,12 +8402,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -8647,12 +8647,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,12 +8980,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -8997,12 +8997,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,17 +9015,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -9557,12 +9557,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -9697,12 +9697,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -9802,12 +9802,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,29 +9855,29 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -9907,12 +9907,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,17 +9925,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,29 +9995,29 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,29 +10030,29 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10100,17 +10100,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
@@ -10152,12 +10152,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10170,29 +10170,29 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10205,29 +10205,29 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,29 +10310,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,29 +10345,29 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,12 +10380,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -10397,12 +10397,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,29 +10415,29 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,29 +10450,29 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -10502,12 +10502,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,29 +10520,29 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,29 +10555,29 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,29 +10590,29 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,29 +10835,29 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10905,29 +10905,29 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10940,29 +10940,29 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10975,29 +10975,29 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11010,29 +11010,29 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11045,29 +11045,29 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11080,29 +11080,29 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11115,29 +11115,29 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11150,29 +11150,29 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11185,29 +11185,29 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11220,29 +11220,29 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11255,29 +11255,29 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11290,29 +11290,29 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11325,29 +11325,29 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11360,29 +11360,29 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11395,29 +11395,29 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11430,29 +11430,29 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11465,50 +11465,85 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D317" t="n">
-        <v>1</v>
-      </c>
-      <c r="E317" t="inlineStr">
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
+      <c r="E318" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
+      <c r="F318" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
+      <c r="G318" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G318"/>
+  <dimension ref="A1:G319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9627,12 +9627,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -9732,12 +9732,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -9837,12 +9837,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,29 +9855,29 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,12 +9925,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -9942,12 +9942,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,17 +9960,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -10012,12 +10012,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,29 +10030,29 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10100,29 +10100,29 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10135,17 +10135,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10205,29 +10205,29 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,29 +10310,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,29 +10345,29 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,29 +10380,29 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,12 +10415,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -10432,12 +10432,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,29 +10450,29 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,29 +10485,29 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -10537,12 +10537,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,29 +10555,29 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,29 +10590,29 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,29 +10835,29 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10905,29 +10905,29 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10940,29 +10940,29 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10975,29 +10975,29 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11010,29 +11010,29 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11045,29 +11045,29 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11080,29 +11080,29 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11115,29 +11115,29 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11150,29 +11150,29 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11185,29 +11185,29 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11220,29 +11220,29 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11255,29 +11255,29 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11290,29 +11290,29 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11325,29 +11325,29 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11360,29 +11360,29 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11395,29 +11395,29 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11430,29 +11430,29 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11465,29 +11465,29 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11500,50 +11500,85 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D318" t="n">
-        <v>1</v>
-      </c>
-      <c r="E318" t="inlineStr">
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1</v>
+      </c>
+      <c r="E319" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
+      <c r="F319" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
+      <c r="G319" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G319"/>
+  <dimension ref="A1:G320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6162,12 +6162,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>CONCOM SOLAR ITALIA 02 SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>CONCOM SOLAR 02</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>CONCOM SOLAR 02</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>CONCOM SOLAR ITALIA 02 SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Perugia</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -6267,12 +6267,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,34 +6320,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6372,17 +6372,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6757,12 +6757,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -8437,12 +8437,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,29 +8455,29 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -8682,12 +8682,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,29 +8805,29 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -9032,12 +9032,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,17 +9050,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -9102,12 +9102,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -9592,12 +9592,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -9767,12 +9767,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -9872,12 +9872,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,29 +9925,29 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -9977,12 +9977,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,17 +9995,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -10047,12 +10047,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10100,29 +10100,29 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10135,29 +10135,29 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10170,17 +10170,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
@@ -10222,12 +10222,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,29 +10310,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,29 +10345,29 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,29 +10380,29 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,29 +10415,29 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -10467,12 +10467,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,29 +10485,29 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,29 +10520,29 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -10572,12 +10572,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,29 +10590,29 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,29 +10835,29 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10905,29 +10905,29 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10940,29 +10940,29 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10975,29 +10975,29 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11010,29 +11010,29 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11045,29 +11045,29 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11080,29 +11080,29 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11115,29 +11115,29 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11150,29 +11150,29 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11185,29 +11185,29 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11220,29 +11220,29 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11255,29 +11255,29 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11290,29 +11290,29 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11325,29 +11325,29 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11360,29 +11360,29 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11395,29 +11395,29 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11430,29 +11430,29 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>CHIRON ENERGY SPV 10</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11465,29 +11465,29 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>REDEN ALFA</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>REDEN ALFA SRL</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11500,29 +11500,29 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Frosinone</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11535,50 +11535,85 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>SOLAR PV 39</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>SOLAR PV 39 SRL</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D319" t="n">
-        <v>1</v>
-      </c>
-      <c r="E319" t="inlineStr">
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1</v>
+      </c>
+      <c r="E320" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
+      <c r="F320" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
+      <c r="G320" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G320"/>
+  <dimension ref="A1:G325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9382,12 +9382,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>SOLAR PV 34 SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>SOLAR PV 34</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>SOLAR PV 34</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>SOLAR PV 34 SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -9417,12 +9417,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>SOLARVIA SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>SOLARVIA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>SOLARVIA</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>SOLARVIA SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>ENVIROSUN SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>ENVIROSUN</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>ENVIROSUN</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>ENVIROSUN SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,29 +9575,29 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>ATLAS STORAGE 13 SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>ATLAS STORAGE 13</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>ATLAS STORAGE 13</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>ATLAS STORAGE 13 SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>CR RINNOVABILI 4</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>CR RINNOVABILI 4</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,29 +9855,29 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,29 +9925,29 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,29 +9960,29 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,29 +9995,29 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,29 +10030,29 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>LANGA SIPSMITH</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -10100,12 +10100,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -10117,12 +10117,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10135,29 +10135,29 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>GRANDE RINNOVABILI SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10170,29 +10170,29 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>ENEL GREEN POWER ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10205,29 +10205,29 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -10275,29 +10275,29 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>GRANDE RINNOVABILI</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>GRANDE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -10310,29 +10310,29 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>ENEL GREEN POWER</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>ENEL GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -10345,29 +10345,29 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10380,29 +10380,29 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -10415,29 +10415,29 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10450,29 +10450,29 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 07 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 05 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -10502,12 +10502,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10520,29 +10520,29 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>RENPV6</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>RENPV6 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10555,29 +10555,29 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AG 37</t>
+          <t>CHIRON ENERGY SPV 07</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>AG 37 SRL</t>
+          <t>CHIRON ENERGY SPV 07 SRL</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -10607,12 +10607,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10625,29 +10625,29 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AIEM GREEN</t>
+          <t>CHIRON ENERGY SPV 05</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>AIEM GREEN SRL</t>
+          <t>CHIRON ENERGY SPV 05 SRL</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>PHOTOSOL</t>
+          <t>RENPV6</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
+          <t>RENPV6 SRL</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10695,29 +10695,29 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>PV 1</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>PV ITALY 1 SRL</t>
+          <t>REPSOL RENEWABLE ENERGIES NORD 1 SRL</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10730,29 +10730,29 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 37</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 37 SRL</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10765,29 +10765,29 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AIEM GREEN</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AIEM GREEN SRL</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10800,29 +10800,29 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13</t>
+          <t>PHOTOSOL</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>ATLAS SOLAR 13 SRL</t>
+          <t>PHOTOSOL ENERGIA ITALIA SRL</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10835,29 +10835,29 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>DOLOMITI MERCATO</t>
+          <t>PV 1</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>DOLOMITI ENERGIA MERCATO SPA</t>
+          <t>PV ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10870,29 +10870,29 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>RERE 62</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>RERE 62 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10905,29 +10905,29 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>DS 34</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>DS ITALIA 34 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10940,29 +10940,29 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>ATLAS SOLAR 13</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>ATLAS SOLAR 13 SRL</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10975,29 +10975,29 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>DOLOMITI MERCATO</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>DOLOMITI ENERGIA MERCATO SPA</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11010,29 +11010,29 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>RERE 62</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>RERE 62 SRL</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11045,29 +11045,29 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>DS 34</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>DS ITALIA 34 SRL</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -11097,12 +11097,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11115,29 +11115,29 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11150,29 +11150,29 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11185,29 +11185,29 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11220,29 +11220,29 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>PERILLO QUAGLIETTA SRL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>PERILLO QUAGLIETTA</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -11255,29 +11255,29 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>PERILLO QUAGLIETTA</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>PERILLO QUAGLIETTA SRL</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -11290,29 +11290,29 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -11325,29 +11325,29 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -11360,29 +11360,29 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -11395,29 +11395,29 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11430,29 +11430,29 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>CHIRON ENERGY SPV 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -11465,29 +11465,29 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>REDEN ALFA</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>REDEN ALFA SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11500,29 +11500,29 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>EGP MAZZOCCHIO SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11535,29 +11535,29 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>SOLAR PV 39</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>SOLAR PV 39 SRL</t>
+          <t>BLUSOLAR SESTO AL REGHENA 1 SRL</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -11570,50 +11570,225 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>RAI WAY</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>RAI WAY SPA</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>CHIRON ENERGY SPV 10 SRL</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>REDEN ALFA</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>REDEN ALFA SRL</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>1</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>EGP MAZZOCCHIO SRL</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>1</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>SOLAR PV 39 SRL</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>1</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>RAI WAY</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>RAI WAY SPA</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D320" t="n">
-        <v>1</v>
-      </c>
-      <c r="E320" t="inlineStr">
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>1</v>
+      </c>
+      <c r="E325" t="inlineStr">
         <is>
           <t>SOLAR PV 1</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
+      <c r="F325" t="inlineStr">
         <is>
           <t>SOLAR PV 1 SRL</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
+      <c r="G325" t="inlineStr">
         <is>
           <t>Milano Sud</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G325"/>
+  <dimension ref="A1:G327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3677,12 +3677,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>TEP RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>TEP RENEWABLES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>TEP RENEWABLES</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>TEP RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>IBVI 8 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>IBVI 8</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>IBVI 8</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>IBVI 8 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3817,12 +3817,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -4097,12 +4097,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4307,12 +4307,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4342,12 +4342,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4412,12 +4412,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4447,12 +4447,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4727,12 +4727,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4902,12 +4902,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5287,12 +5287,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SAN GIORGIO JONICO SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SKI 09</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SKI 09 SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>WOOD SOLARE</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>WOOD SOLARE ITALIA SRL</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ACEA SOLAR</t>
+          <t>WOOD SOLARE</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ACEA SOLAR SRL</t>
+          <t>WOOD SOLARE ITALIA SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA</t>
+          <t>SOLARIA PROMOZIONE SVILUPPO FOTOVOLTAICO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>LUMINORA SPARPAGLIATA SRL</t>
+          <t>SOLARIA PROMOZIONE E SVILUPPO FOTOVOLTAICO SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO</t>
+          <t>ACEA SOLAR</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>APOLLO SAN SEVERO SRL</t>
+          <t>ACEA SOLAR SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10</t>
+          <t>LUMINORA SPARPAGLIATA</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 10 SRL</t>
+          <t>LUMINORA SPARPAGLIATA SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2</t>
+          <t>APOLLO SAN SEVERO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>GR VALUE BRINDISI 2 SRL</t>
+          <t>APOLLO SAN SEVERO SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1</t>
+          <t>ALTA CAPITAL 10</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>OPDENERGY TAVOLIERE 1 SRL</t>
+          <t>ALTA CAPITAL 10 SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO</t>
+          <t>GR VALUE BRINDISI 2</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY VENTUNO SRL</t>
+          <t>GR VALUE BRINDISI 2 SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE</t>
+          <t>OPDENERGY TAVOLIERE 1</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD DUE SRL</t>
+          <t>OPDENERGY TAVOLIERE 1 SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>MESAGNE</t>
+          <t>SOLAR ENERGY VENTUNO</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MESAGNE SRL</t>
+          <t>SOLAR ENERGY VENTUNO SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6022,12 +6022,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>CCEN IRSINA</t>
+          <t>RINNOVABILI SUD DUE</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CCEN IRSINA SRL</t>
+          <t>RINNOVABILI SUD DUE SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S2SE TRE SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>S2SE TRE</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>S2SE TRE</t>
+          <t>MESAGNE</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>S2SE TRE SRL</t>
+          <t>MESAGNE SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3 SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3</t>
+          <t>CCEN IRSINA</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>EEC SOLAR 3 SRL</t>
+          <t>CCEN IRSINA SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>INE NARDO' SRL</t>
+          <t>S2SE TRE SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>INE NARDO</t>
+          <t>S2SE TRE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>INE NARDO</t>
+          <t>S2SE TRE</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>INE NARDO' SRL</t>
+          <t>S2SE TRE SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CONCOM SOLAR ITALIA 02 SRL</t>
+          <t>EEC SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CONCOM SOLAR 02</t>
+          <t>EEC SOLAR 3</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CONCOM SOLAR 02</t>
+          <t>EEC SOLAR 3</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CONCOM SOLAR ITALIA 02 SRL</t>
+          <t>EEC SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>INE NARDO' SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>INE NARDO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>INE NARDO</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>INE NARDO' SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>CONCOM SOLAR ITALIA 02 SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>CONCOM SOLAR 02</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>CONCOM SOLAR 02</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>CONCOM SOLAR ITALIA 02 SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Perugia</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6372,17 +6372,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,34 +6425,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6652,12 +6652,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>DOMUSNOVAS SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>DOMUSNOVAS</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>DOMUSNOVAS SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>OPR SUN 30</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>OPR SUN 30 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>GREEN GENIUS UTILITY 15</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>OPR SUN 30</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>OPR SUN 30 SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>GREEN GENIUS UTILITY 15</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>GREEN GENIUS ITALY UTILITY 15 SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SONNEDIX MAG SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7002,12 +7002,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>SONNEDIX MAG</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>SONNEDIX MAG SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7107,12 +7107,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>E24E</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>E24E SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>E24E</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>E24E SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>IPC SOLAR BELT SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>REVALUE PV 11</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>REVALUE PV 11 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7457,12 +7457,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI</t>
+          <t>IPC SOLAR BELT</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SWISSPOWER RINNOVABILI SRL</t>
+          <t>IPC SOLAR BELT SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>APICE VERDE</t>
+          <t>REVALUE PV 11</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>APICE VERDE SRL</t>
+          <t>REVALUE PV 11 SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL</t>
+          <t>SWISSPOWER RINNOVABILI</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>RONCELLO CAPITAL SRL</t>
+          <t>SWISSPOWER RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>APICE VERDE</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>APICE VERDE SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>ACHEON</t>
+          <t>RONCELLO CAPITAL</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ACHEON SRL</t>
+          <t>RONCELLO CAPITAL SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SOTTOCOLLE SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACHEON</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACHEON SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SOTTOCOLLE</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SOTTOCOLLE SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,17 +7860,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -7912,12 +7912,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SMARTENERGYIT2104 SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SMARTENERGYIT2104</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SMARTENERGYIT2104 SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,29 +8175,29 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8210,29 +8210,29 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8245,29 +8245,29 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8280,29 +8280,29 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8315,29 +8315,29 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8350,29 +8350,29 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -8472,12 +8472,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8525,29 +8525,29 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8595,29 +8595,29 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>ELPI</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>ELPI SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8630,29 +8630,29 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ELPI</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ELPI SRL</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8700,29 +8700,29 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8735,29 +8735,29 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -8822,12 +8822,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8840,29 +8840,29 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8875,29 +8875,29 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8945,29 +8945,29 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8980,29 +8980,29 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -9015,29 +9015,29 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9085,29 +9085,29 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9155,29 +9155,29 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9190,29 +9190,29 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9225,29 +9225,29 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI SOLARE</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FISCAGLIA AGRI-SOLARE SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9260,29 +9260,29 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>FERRARA SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>CEDRO</t>
+          <t>FISCAGLIA AGRI SOLARE</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CEDRO SRL</t>
+          <t>FISCAGLIA AGRI-SOLARE SRL</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -9312,12 +9312,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9330,29 +9330,29 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BONDENO PV</t>
+          <t>FERRARA SOLAR</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
+          <t>FERRARA SOLAR SRL</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9365,29 +9365,29 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16</t>
+          <t>CEDRO</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>ICUBE DEVELOPMENT 16 SRL</t>
+          <t>CEDRO SRL</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SOLAR PV 34 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SOLAR PV 34</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9400,29 +9400,29 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>SOLAR PV 34</t>
+          <t>TEP RENEWABLES BONDENO PV</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SOLAR PV 34 SRL</t>
+          <t>TEP RENEWABLES (BONDENO PV) SRL</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SOLARVIA SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SOLARVIA</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>SOLARVIA</t>
+          <t>ICUBE DEVELOPMENT 16</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SOLARVIA SRL</t>
+          <t>ICUBE DEVELOPMENT 16 SRL</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ENVIROSUN SRL</t>
+          <t>SOLAR PV 34 SRL</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ENVIROSUN</t>
+          <t>SOLAR PV 34</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9470,29 +9470,29 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>ENVIROSUN</t>
+          <t>SOLAR PV 34</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>ENVIROSUN SRL</t>
+          <t>SOLAR PV 34 SRL</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>SOLARVIA SRL</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>SOLARVIA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9505,29 +9505,29 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>SOLARVIA</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>SOLARVIA SRL</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ENVIROSUN SRL</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>ENVIROSUN</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>ENVIROSUN</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ENVIROSUN SRL</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>VERBUND GREEN POWER ITALIA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -9592,12 +9592,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9610,29 +9610,29 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>JUWI DEVELOPMENT 15 SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ATLAS STORAGE 13 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>ATLAS STORAGE 13</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9645,29 +9645,29 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>ATLAS STORAGE 13</t>
+          <t>VERBUND GREEN POWER</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>ATLAS STORAGE 13 SRL</t>
+          <t>VERBUND GREEN POWER ITALIA SRL</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9680,29 +9680,29 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI DEVELOPMENT 15</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI DEVELOPMENT 15 SRL</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>ATLAS STORAGE 13 SRL</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>ATLAS STORAGE 13</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9715,29 +9715,29 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>ATLAS STORAGE 13</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>ATLAS STORAGE 13 SRL</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9750,29 +9750,29 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9785,29 +9785,29 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CR RINNOVABILI 4 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9855,29 +9855,29 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>CR RINNOVABILI 4</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY</t>
+          <t>CR RINNOVABILI 4</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>OPERATION ENERGY S.R.L.</t>
+          <t>CR RINNOVABILI 4 SRL</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9925,29 +9925,29 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9960,29 +9960,29 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34</t>
+          <t>OPERATION ENERGY</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>ORTA ENERGY 34 SRL</t>
+          <t>OPERATION ENERGY S.R.L.</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9995,29 +9995,29 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10030,29 +10030,29 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH</t>
+          <t>ORTA ENERGY 34</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>LANGA SIPSMITH SRL</t>
+          <t>ORTA ENERGY 34 SRL</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10065,29 +10065,29 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LANGA SIPSMITH SRL</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>LANGA SIPSMITH</t>
        